--- a/data/trans_bre/IP19C01-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C01-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,16; 10,02</t>
+          <t>-15,09; 11,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-20,33; 10,54</t>
+          <t>-18,82; 9,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 24,24</t>
+          <t>-7,74; 25,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-21,4; 0,13</t>
+          <t>-21,19; 0,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-19,12; 13,65</t>
+          <t>-17,84; 16,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,75; 14,66</t>
+          <t>-22,74; 12,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 43,02</t>
+          <t>-10,57; 42,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-24,48; -0,28</t>
+          <t>-24,03; 0,59</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,6; 19,25</t>
+          <t>-19,12; 17,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,25; 12,48</t>
+          <t>-16,23; 12,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 16,66</t>
+          <t>-10,18; 16,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,52; 6,37</t>
+          <t>-14,4; 6,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-23,14; 33,02</t>
+          <t>-24,91; 30,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,8; 18,83</t>
+          <t>-20,07; 18,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 24,84</t>
+          <t>-11,82; 23,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-16,01; 7,69</t>
+          <t>-15,95; 7,58</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-21,92; 12,18</t>
+          <t>-23,46; 10,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 19,12</t>
+          <t>-10,64; 19,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,57; 10,29</t>
+          <t>-22,79; 8,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 26,92</t>
+          <t>-14,55; 25,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-28,75; 17,16</t>
+          <t>-30,72; 15,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 29,68</t>
+          <t>-13,37; 30,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-23,41; 14,29</t>
+          <t>-25,32; 11,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-15,14; 49,55</t>
+          <t>-17,83; 45,54</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,53; 8,81</t>
+          <t>-11,66; 9,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,5; 5,51</t>
+          <t>-15,91; 4,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-14,87; 5,43</t>
+          <t>-14,69; 4,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 20,24</t>
+          <t>0,02; 20,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,47; 12,93</t>
+          <t>-14,94; 14,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,94; 7,8</t>
+          <t>-19,69; 6,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,25; 7,83</t>
+          <t>-18,43; 6,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 29,78</t>
+          <t>0,08; 32,38</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-26,98; 2,13</t>
+          <t>-27,23; 0,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,42; 10,7</t>
+          <t>-12,79; 11,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-26,51; -1,98</t>
+          <t>-26,89; -2,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-23,07; 4,08</t>
+          <t>-22,83; 2,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-36,57; 3,23</t>
+          <t>-37,07; 1,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-20,67; 18,36</t>
+          <t>-18,0; 19,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-31,85; -3,11</t>
+          <t>-32,44; -3,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-25,51; 4,75</t>
+          <t>-25,5; 3,53</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-35,16; 0,49</t>
+          <t>-33,04; -0,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-20,89; 11,79</t>
+          <t>-22,15; 11,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 25,61</t>
+          <t>-11,04; 23,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-13,79; 13,68</t>
+          <t>-14,09; 11,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-41,86; -0,46</t>
+          <t>-40,0; -1,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-23,64; 15,87</t>
+          <t>-24,87; 14,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-15,38; 44,74</t>
+          <t>-14,57; 41,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-15,08; 17,64</t>
+          <t>-15,19; 14,99</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 0,14</t>
+          <t>-10,87; 0,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 2,45</t>
+          <t>-8,94; 2,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 2,16</t>
+          <t>-8,37; 2,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 4,24</t>
+          <t>-6,17; 4,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-15,33; 0,2</t>
+          <t>-14,6; 0,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 3,26</t>
+          <t>-11,52; 3,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 2,92</t>
+          <t>-10,65; 3,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 5,29</t>
+          <t>-7,15; 5,52</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C01-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C01-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,09; 11,83</t>
+          <t>-15,28; 11,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,82; 9,07</t>
+          <t>-19,17; 11,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 25,18</t>
+          <t>-7,21; 25,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-21,19; 0,5</t>
+          <t>-21,25; 0,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-17,84; 16,19</t>
+          <t>-18,25; 15,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,74; 12,91</t>
+          <t>-23,31; 16,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,57; 42,95</t>
+          <t>-9,61; 43,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-24,03; 0,59</t>
+          <t>-24,08; -0,26</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-19,12; 17,21</t>
+          <t>-16,06; 17,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,23; 12,5</t>
+          <t>-15,91; 13,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 16,29</t>
+          <t>-10,86; 15,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 6,36</t>
+          <t>-14,58; 6,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-24,91; 30,54</t>
+          <t>-21,39; 30,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,07; 18,17</t>
+          <t>-19,91; 20,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 23,67</t>
+          <t>-12,39; 22,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-15,95; 7,58</t>
+          <t>-15,83; 7,92</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-23,46; 10,64</t>
+          <t>-22,07; 9,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 19,6</t>
+          <t>-9,54; 21,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-22,79; 8,86</t>
+          <t>-20,72; 10,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,55; 25,55</t>
+          <t>-13,52; 27,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-30,72; 15,74</t>
+          <t>-28,09; 15,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 30,89</t>
+          <t>-11,26; 33,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-25,32; 11,86</t>
+          <t>-23,58; 13,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-17,83; 45,54</t>
+          <t>-16,04; 49,07</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 9,5</t>
+          <t>-12,12; 8,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,91; 4,85</t>
+          <t>-15,29; 4,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-14,69; 4,45</t>
+          <t>-15,07; 4,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,02; 20,88</t>
+          <t>0,44; 20,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 14,0</t>
+          <t>-15,62; 12,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,69; 6,5</t>
+          <t>-18,93; 6,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,43; 6,09</t>
+          <t>-18,93; 5,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 32,38</t>
+          <t>0,58; 30,39</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-27,23; 0,84</t>
+          <t>-25,43; 1,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 11,33</t>
+          <t>-13,78; 11,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-26,89; -2,89</t>
+          <t>-27,19; -3,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-22,83; 2,94</t>
+          <t>-22,1; 3,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-37,07; 1,51</t>
+          <t>-35,43; 2,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,0; 19,81</t>
+          <t>-19,15; 20,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-32,44; -3,96</t>
+          <t>-32,82; -4,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-25,5; 3,53</t>
+          <t>-24,27; 4,79</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-33,04; -0,67</t>
+          <t>-35,25; -2,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-22,15; 11,11</t>
+          <t>-20,29; 11,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 23,82</t>
+          <t>-11,47; 23,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-14,09; 11,86</t>
+          <t>-13,8; 13,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-40,0; -1,13</t>
+          <t>-42,23; -4,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-24,87; 14,17</t>
+          <t>-23,03; 14,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-14,57; 41,46</t>
+          <t>-14,65; 41,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-15,19; 14,99</t>
+          <t>-15,1; 17,27</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 0,21</t>
+          <t>-10,89; 0,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 2,58</t>
+          <t>-8,15; 2,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,37; 2,25</t>
+          <t>-9,23; 1,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 4,35</t>
+          <t>-5,86; 4,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 0,26</t>
+          <t>-14,34; 0,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 3,53</t>
+          <t>-10,48; 3,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,65; 3,13</t>
+          <t>-11,76; 2,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 5,52</t>
+          <t>-7,09; 5,39</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C01-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C01-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-10,42</t>
+          <t>-10,79</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-12,08%</t>
+          <t>-12,6%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,28; 11,44</t>
+          <t>-16,16; 10,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,17; 11,09</t>
+          <t>-20,33; 10,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 25,18</t>
+          <t>-6,93; 24,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-21,25; 0,1</t>
+          <t>-22,23; -0,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,25; 15,82</t>
+          <t>-19,12; 13,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-23,31; 16,31</t>
+          <t>-24,75; 14,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 43,1</t>
+          <t>-8,86; 43,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-24,08; -0,26</t>
+          <t>-25,13; 0,03</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-3,9</t>
+          <t>-4,42</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-4,46%</t>
+          <t>-5,02%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 17,71</t>
+          <t>-17,6; 19,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,91; 13,67</t>
+          <t>-16,25; 12,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,86; 15,62</t>
+          <t>-9,28; 16,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,58; 6,55</t>
+          <t>-14,66; 5,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-21,39; 30,63</t>
+          <t>-23,14; 33,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,91; 20,35</t>
+          <t>-19,8; 18,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 22,07</t>
+          <t>-10,99; 24,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-15,83; 7,92</t>
+          <t>-16,44; 7,01</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,72</t>
+          <t>6,69</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-22,07; 9,85</t>
+          <t>-21,92; 12,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 21,09</t>
+          <t>-10,49; 19,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 10,29</t>
+          <t>-20,57; 10,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,52; 27,65</t>
+          <t>-12,3; 25,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-28,09; 15,15</t>
+          <t>-28,75; 17,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,26; 33,76</t>
+          <t>-12,83; 29,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-23,58; 13,55</t>
+          <t>-23,41; 14,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-16,04; 49,07</t>
+          <t>-16,03; 43,54</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10,56</t>
+          <t>8,64</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,12; 8,8</t>
+          <t>-10,53; 8,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,29; 4,72</t>
+          <t>-15,5; 5,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 4,27</t>
+          <t>-14,87; 5,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 20,29</t>
+          <t>-1,81; 18,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-15,62; 12,81</t>
+          <t>-13,47; 12,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,93; 6,33</t>
+          <t>-18,94; 7,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,93; 5,94</t>
+          <t>-18,25; 7,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 30,39</t>
+          <t>-2,28; 26,78</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-8,5</t>
+          <t>-4,46</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-9,7%</t>
+          <t>-5,12%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-25,43; 1,72</t>
+          <t>-26,98; 2,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,78; 11,93</t>
+          <t>-15,42; 10,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-27,19; -3,32</t>
+          <t>-26,51; -1,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-22,1; 3,92</t>
+          <t>-16,47; 7,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-35,43; 2,56</t>
+          <t>-36,57; 3,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,15; 20,21</t>
+          <t>-20,67; 18,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-32,82; -4,62</t>
+          <t>-31,85; -3,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-24,27; 4,79</t>
+          <t>-18,15; 8,57</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1,3</t>
+          <t>-1,04</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-1,51%</t>
+          <t>-1,21%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-35,25; -2,81</t>
+          <t>-35,16; 0,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-20,29; 11,89</t>
+          <t>-20,89; 11,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 23,94</t>
+          <t>-12,28; 25,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 13,78</t>
+          <t>-13,81; 13,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-42,23; -4,19</t>
+          <t>-41,86; -0,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-23,03; 14,69</t>
+          <t>-23,64; 15,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-14,65; 41,83</t>
+          <t>-15,38; 44,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-15,1; 17,27</t>
+          <t>-14,88; 17,86</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,85</t>
+          <t>-0,8</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-1,03%</t>
+          <t>-0,97%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 0,41</t>
+          <t>-11,44; 0,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 2,58</t>
+          <t>-8,88; 2,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 1,94</t>
+          <t>-8,87; 2,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 4,35</t>
+          <t>-5,5; 4,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,34; 0,64</t>
+          <t>-15,33; 0,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,48; 3,51</t>
+          <t>-11,63; 3,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 2,69</t>
+          <t>-11,44; 2,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 5,39</t>
+          <t>-6,48; 5,31</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C01-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C01-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-2,95</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-4,97</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8,71</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-10,79</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-3,73%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-6,41%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,02%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-12,6%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-2.946065494945782</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-4.974725050808249</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>8.707101864937339</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-10.7880442378136</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.03727235867135314</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.06405722807013609</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.1302131220065353</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.1259811490174444</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-16,16; 10,02</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-20,33; 10,54</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-6,93; 24,24</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-22,23; -0,11</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-19,12; 13,65</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-24,75; 14,66</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-8,86; 43,02</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-25,13; 0,03</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-16.15872280354866</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-20.32883846379412</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-6.92652526739274</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-22.22725439823378</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.1911619028716239</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.2474939759617123</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.08863036258160119</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.2513372143471934</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>10.02061080525365</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>10.53538448809793</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>24.24020657163415</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>-0.106900296833363</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.1365103867797368</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.1465808499894392</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.4301562229978511</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.0003454826753442875</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,26</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-1,48</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,93</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-4,42</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-1,96%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>3,78%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-5,02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-17,6; 19,25</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-16,25; 12,48</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-9,28; 16,66</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-14,66; 5,88</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-23,14; 33,02</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-19,8; 18,83</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-10,99; 24,84</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-16,44; 7,01</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.2611091488858741</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-1.475839407356383</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>2.934507214064241</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-4.423868498291106</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.003897716985228116</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.01962597514795966</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.03776241570572531</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.05024135385134879</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-4,78</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4,79</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-5,55</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6,69</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-6,63%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,55%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-6,66%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>9,58%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-17.59693114495515</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-16.24881506327027</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-9.282624168347095</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-14.65708546547949</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.2314142702667126</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.1980405301866448</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.1099448430634602</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.1643737010825497</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-21,92; 12,18</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-10,49; 19,12</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-20,57; 10,29</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-12,3; 25,75</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-28,75; 17,16</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-12,83; 29,68</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-23,41; 14,29</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-16,03; 43,54</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>19.24607460692282</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>12.48124991620806</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>16.66321078615031</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>5.877713388286594</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.3302046330755912</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.1883437175477256</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.2483522881633766</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.07006646817353346</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +819,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-1,26</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-5,27</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-5,47</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8,64</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-1,72%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-6,82%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-7,19%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11,45%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-4.782716532975195</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>4.788726221289796</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-5.549389573292995</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>6.690518960653091</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.06628664710955179</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.06548687097802848</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.06659408374471204</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.0957800289636411</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-10,53; 8,81</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-15,5; 5,51</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-14,87; 5,43</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-1,81; 18,44</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-13,47; 12,93</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-18,94; 7,8</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-18,25; 7,83</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-2,28; 26,78</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-21.91974699329158</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-10.48723933969543</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-20.57423367228545</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-12.30338041823342</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.2874868291492085</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.1283464928097762</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.2341273979847588</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.1602640340551305</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>12.17552584535733</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>19.12044947146404</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>10.28512067682968</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>25.74768123100333</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.171613680039045</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.2968169085670829</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.1428943765909969</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.4353857113511734</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-12,28</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-1,8</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-15,16</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-4,46</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-18,05%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-2,71%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-19,19%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-5,12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-26,98; 2,13</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-15,42; 10,7</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-26,51; -1,98</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-16,47; 7,01</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-36,57; 3,23</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-20,67; 18,36</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-31,85; -3,11</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-18,15; 8,57</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-1.263864671298298</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-5.269229774899909</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-5.469523978542301</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>8.6375712787914</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.01723485809601252</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.06815625178236012</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.07193562013065426</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.1145452804359594</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-18,07</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-4,5</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>7,38</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-1,04</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-23,17%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-5,39%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>10,69%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-1,21%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-10.53081959728339</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-15.49586246829603</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-14.86513145999749</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-1.807992596817667</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.1347080718835919</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.1894021950505175</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.1824742613874596</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.02277704209382924</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-35,16; 0,49</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-20,89; 11,79</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-12,28; 25,61</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-13,81; 13,78</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-41,86; -0,46</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-23,64; 15,87</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-15,38; 44,74</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-14,88; 17,86</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>8.808831903880423</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>5.514523209377168</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>5.42564663038265</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>18.44140276098651</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.1292975615525034</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.07801713519219866</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.07832698246146128</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.2678362923108381</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +1019,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-5,31</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-3,04</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-3,0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,8</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-7,31%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-4,06%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-3,96%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-0,97%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>-12.28456453798993</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-1.797455640056156</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-15.15853870022066</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-4.458303927192508</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.180548654840012</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.02705602673571049</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.1919242843053576</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.05121294222090319</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-11,44; 0,14</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-8,88; 2,45</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-8,87; 2,16</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-5,5; 4,27</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-15,33; 0,2</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-11,63; 3,26</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-11,44; 2,92</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-6,48; 5,31</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-26.98067091705358</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-15.41945354964278</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-26.50850984199847</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-16.4726036832657</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.3657218130597716</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.206679099562525</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.3184798411286418</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.1814961363203657</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2.127243180066374</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>10.7040979299057</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>-1.978742615763442</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>7.010650666440823</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.03230543017010323</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.1835765215205149</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>-0.03111232767737998</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.08572883806680283</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-18.07427905822497</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-4.503515638832756</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>7.381309024143922</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-1.043567835867687</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.2317200172135623</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.05390756450380659</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>0.1069043160181943</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>-0.01209276354711229</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-35.16341255219505</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-20.88609316817503</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-12.27637353063267</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-13.80617039210159</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.4185707366719716</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.2363694697500542</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>-0.153831122646234</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>-0.1487733711731289</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0.4929547941467304</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>11.78661910251192</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>25.61240772477936</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>13.78495543471518</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>-0.004622473699630531</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.1587221494861486</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>0.4474361250009641</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>0.1785888751475259</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-5.312905220976916</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-3.039377574509639</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-2.998220418023767</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-0.7958260510962045</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.07309155623767637</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.04058901400908366</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>-0.03962376006543629</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>-0.009655349222912252</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-11.44385371475664</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-8.87615691788579</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-8.873387634470975</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-5.495816449865036</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.1532605355086006</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.1163339335856726</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.1143869076790858</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.06479195224028148</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.1408230233275527</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>2.448755011753127</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>2.160689914937527</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>4.271759415376319</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.001960378786591677</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.0326391555012662</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.02919243611163531</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.05308181291635808</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1317,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
